--- a/data/supplementary_tables/Supplementary Table 16.xlsx
+++ b/data/supplementary_tables/Supplementary Table 16.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10719"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10726"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/linweili/Important_files/课题进展/Eukaryotes_Asgard_TACK/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/linweili/Important_files/课题进展/Nature_submission_verified_red/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E063E857-FBD0-0343-BDD5-B7B49FC909D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41BED7D9-2F3B-3947-99FF-CE77075D22EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="640" windowWidth="30240" windowHeight="17420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="237">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="239">
   <si>
     <t>Protein_Short_Name</t>
   </si>
@@ -64,15 +64,9 @@
     <t>Oligopeptide transporter</t>
   </si>
   <si>
-    <t>Probably</t>
-  </si>
-  <si>
     <t>ppGalNAc-T6</t>
   </si>
   <si>
-    <t>Involved in the binding of</t>
-  </si>
-  <si>
     <t>Aerotolerance regulator N-terminal</t>
   </si>
   <si>
@@ -94,30 +88,15 @@
     <t>Uracil-DNA glycosylase</t>
   </si>
   <si>
-    <t>Catalyzes the hydrolysis of the</t>
-  </si>
-  <si>
     <t>Formation of pseudouridine at positions</t>
   </si>
   <si>
     <t>DNA photolyase family</t>
   </si>
   <si>
-    <t>Binds to 23S rRNA.</t>
-  </si>
-  <si>
     <t>Proteasome core subunit</t>
   </si>
   <si>
-    <t>Could be</t>
-  </si>
-  <si>
-    <t>COMPASS (Set1C) complex that specifically</t>
-  </si>
-  <si>
-    <t>Four repeated domains in the</t>
-  </si>
-  <si>
     <t>Glucose-6-phosphate Isomerase</t>
   </si>
   <si>
@@ -145,9 +124,6 @@
     <t>Archaeal Rpom Eukaryotic RPA12 RPB9</t>
   </si>
   <si>
-    <t>Gamma-secretase Complex, An Endoprotease...</t>
-  </si>
-  <si>
     <t>Binds to the 23S Rrna</t>
   </si>
   <si>
@@ -163,15 +139,6 @@
     <t>TIGRFAM DMSO reductase family type</t>
   </si>
   <si>
-    <t>Uptake of acetate and succinate.</t>
-  </si>
-  <si>
-    <t>Catalyzes the last two sequential</t>
-  </si>
-  <si>
-    <t>Binds 16S rRNA</t>
-  </si>
-  <si>
     <t>Eukaryotic Ribosomal Protein El34 Family</t>
   </si>
   <si>
@@ -181,12 +148,6 @@
     <t>Chromosome 15 open reading frame 41</t>
   </si>
   <si>
-    <t>Large family of predicted...</t>
-  </si>
-  <si>
-    <t>Predicted SAM-dependent RNA...</t>
-  </si>
-  <si>
     <t>MIP aquaporin (TC 1.A.8) family</t>
   </si>
   <si>
@@ -202,27 +163,15 @@
     <t>JAB/MPN domain</t>
   </si>
   <si>
-    <t>Dual specificity protein phosphatase,...</t>
-  </si>
-  <si>
     <t>Serine Threonine Protein Kinase</t>
   </si>
   <si>
-    <t>Haloacid dehalogenase domain protein...</t>
-  </si>
-  <si>
     <t>Putative diphthamide synthesis protein</t>
   </si>
   <si>
-    <t>Promotes the exchange of GDP</t>
-  </si>
-  <si>
     <t>Sulphite efflux pump</t>
   </si>
   <si>
-    <t>Binds double-stranded DNA tightly but</t>
-  </si>
-  <si>
     <t>THUMP domain-containing protein 1</t>
   </si>
   <si>
@@ -259,18 +208,12 @@
     <t>UPF0696 protein C11orf68 homolog</t>
   </si>
   <si>
-    <t>Mannose-6-phosphate Isomerase Type 2...</t>
-  </si>
-  <si>
     <t>Eukaryotic Ribosomal Protein El33 Family</t>
   </si>
   <si>
     <t>Function in general translation initiation</t>
   </si>
   <si>
-    <t>Probable Brix domain-containing ribosomal...</t>
-  </si>
-  <si>
     <t>'Cold-shock' DNA-binding domain</t>
   </si>
   <si>
@@ -382,15 +325,9 @@
     <t>Ribosomal Protein S15</t>
   </si>
   <si>
-    <t>Catalyzes the interconversion of...</t>
-  </si>
-  <si>
     <t>NDP-sugar transferase</t>
   </si>
   <si>
-    <t>Sodium Neurotransmitter Symporter (snf)...</t>
-  </si>
-  <si>
     <t>AP-5 complex subunit beta-1</t>
   </si>
   <si>
@@ -400,9 +337,6 @@
     <t>PFAM MaoC domain protein dehydratase</t>
   </si>
   <si>
-    <t>Retinal pigment epithelial membrane...</t>
-  </si>
-  <si>
     <t>Binds directly to 23S rRNA.</t>
   </si>
   <si>
@@ -421,9 +355,6 @@
     <t>PUA domain</t>
   </si>
   <si>
-    <t>Methenyltetrahydrofolate Synthetase...</t>
-  </si>
-  <si>
     <t>Superoxide dismutase</t>
   </si>
   <si>
@@ -475,9 +406,6 @@
     <t>Molybdate transporter of MFS superfamily</t>
   </si>
   <si>
-    <t>PFAM nucleic acid binding, OB-fold,</t>
-  </si>
-  <si>
     <t>Eif-2</t>
   </si>
   <si>
@@ -526,21 +454,12 @@
     <t>Histone lysine methyltransferase</t>
   </si>
   <si>
-    <t>Determination of Stomach Left/right...</t>
-  </si>
-  <si>
-    <t>Small Gtpase Superfamily.</t>
-  </si>
-  <si>
     <t>GTP-binding protein 1</t>
   </si>
   <si>
     <t>Endonuclease</t>
   </si>
   <si>
-    <t>One of the primary rRNA</t>
-  </si>
-  <si>
     <t>Macrophage migration inhibitory</t>
   </si>
   <si>
@@ -580,15 +499,9 @@
     <t>Peptidase S1B Family</t>
   </si>
   <si>
-    <t>N-acetylglucosaminyl-proteoglycan...</t>
-  </si>
-  <si>
     <t>Involved in regulation of DNA replication</t>
   </si>
   <si>
-    <t>Phosphatidylinositol glycan anchor...</t>
-  </si>
-  <si>
     <t>Hydrolase, Family 1</t>
   </si>
   <si>
@@ -598,9 +511,6 @@
     <t>Regulation of DNA Damage Checkpoint</t>
   </si>
   <si>
-    <t>Hydroxymethylglutaryl-CoA reductase,...</t>
-  </si>
-  <si>
     <t>Binds to the 50S ribosomal</t>
   </si>
   <si>
@@ -613,66 +523,33 @@
     <t>Gelsolin homology domain</t>
   </si>
   <si>
-    <t>Protein N-acetylglucosaminyltransferase...</t>
-  </si>
-  <si>
-    <t>Protein-glutamine...</t>
-  </si>
-  <si>
     <t>Tyrosyl-dna Phosphodiesterase 2</t>
   </si>
   <si>
     <t>Universal Ribosomal Protein Us9 Family</t>
   </si>
   <si>
-    <t>Gene with more than two</t>
-  </si>
-  <si>
     <t>Serine threonine protein kinase</t>
   </si>
   <si>
-    <t>In elementary bodies (EBs, the</t>
-  </si>
-  <si>
-    <t>Acts as a Ras effector</t>
-  </si>
-  <si>
     <t>LURP-one-related</t>
   </si>
   <si>
     <t>ATP-dependent DNA helicase</t>
   </si>
   <si>
-    <t>DNA-directed RNA polymerases I, II,</t>
-  </si>
-  <si>
-    <t>Prostaglandin f2-alpha synthase...</t>
-  </si>
-  <si>
     <t>Eukaryotic Ribosomal Protein El21 Family</t>
   </si>
   <si>
-    <t>Required for pre-18S rRNA processing.</t>
-  </si>
-  <si>
     <t>Transposase</t>
   </si>
   <si>
-    <t>Involved in targeting and insertion</t>
-  </si>
-  <si>
     <t>SWR1 complex</t>
   </si>
   <si>
-    <t>S-adenosyl-L-methionine-dependent...</t>
-  </si>
-  <si>
     <t>ADP-ribosylation factor-like protein</t>
   </si>
   <si>
-    <t>Eca and bai are essential,</t>
-  </si>
-  <si>
     <t>Rho guanine nucleotide exchange factor</t>
   </si>
   <si>
@@ -682,30 +559,12 @@
     <t>Piwi</t>
   </si>
   <si>
-    <t>Catalyzes the GTP-dependent ribosomal...</t>
-  </si>
-  <si>
-    <t>Involved in the secretory pathway</t>
-  </si>
-  <si>
-    <t>Catalyzes the hydrolysis of inorganic</t>
-  </si>
-  <si>
-    <t>Catalyzes the attachment of glycine</t>
-  </si>
-  <si>
     <t>Binds to the 23S rRNA</t>
   </si>
   <si>
-    <t>Integrins alpha-1 beta-1, alpha-2 beta-1,</t>
-  </si>
-  <si>
     <t>K homology RNA-binding domain</t>
   </si>
   <si>
-    <t>May be</t>
-  </si>
-  <si>
     <t>DNA repair helicase</t>
   </si>
   <si>
@@ -731,13 +590,160 @@
   </si>
   <si>
     <t>Supplementary Table 16 | ESP short names in Euryarchaeota: aggregated genome detection counts before and after decontamination and corresponding loss rates</t>
+  </si>
+  <si>
+    <t>γ-secretase subunit</t>
+  </si>
+  <si>
+    <t>Predicted nucleotide-binding domain family</t>
+  </si>
+  <si>
+    <t>SAM-dependent RNA methyltransferase</t>
+  </si>
+  <si>
+    <t>DUSP (N-terminal)</t>
+  </si>
+  <si>
+    <t>HAD hydrolase (type 3)</t>
+  </si>
+  <si>
+    <t>Mannose-6-phosphate isomerase</t>
+  </si>
+  <si>
+    <t>Brix domain protein</t>
+  </si>
+  <si>
+    <t>MtnA / MRI1</t>
+  </si>
+  <si>
+    <t>NSS / SNF transporter</t>
+  </si>
+  <si>
+    <t>RPE membrane protein</t>
+  </si>
+  <si>
+    <t>MTHFS</t>
+  </si>
+  <si>
+    <t>Stomach left–right asymmetry determination</t>
+  </si>
+  <si>
+    <t>Small Gtpase Superfamily</t>
+  </si>
+  <si>
+    <t>β4-Glucuronosyltransferase activity</t>
+  </si>
+  <si>
+    <t>PIG-M</t>
+  </si>
+  <si>
+    <t>Degradative HMG-CoA reductase</t>
+  </si>
+  <si>
+    <t>Protein N-acetylglucosaminyltransferase activity</t>
+  </si>
+  <si>
+    <t>Protein-glutamine γ-glutamyltransferase involved in peptide cross-linking</t>
+  </si>
+  <si>
+    <t>PGF₂α synthase / Arabinose DH</t>
+  </si>
+  <si>
+    <t>TYW3</t>
+  </si>
+  <si>
+    <t>Catalyzes GTP-dependent ribosomal translocation during translation elongation</t>
+  </si>
+  <si>
+    <t>Nitrate/nitrite transporter</t>
+  </si>
+  <si>
+    <t>tRNA–ribosome binding factor</t>
+  </si>
+  <si>
+    <t>Hydrolyzes reactive intermediates of riboflavin biosynthesis</t>
+  </si>
+  <si>
+    <t>Ribosomal protein L24</t>
+  </si>
+  <si>
+    <t>Ribosomal protein L14</t>
+  </si>
+  <si>
+    <t>tRNA pseudouridine synthase</t>
+  </si>
+  <si>
+    <t>Catalytic subunit of the COMPASS complex that methylates H3K4</t>
+  </si>
+  <si>
+    <t>Fasciclin domain protein</t>
+  </si>
+  <si>
+    <t>Acetate/succinate transporter</t>
+  </si>
+  <si>
+    <t>GlmU</t>
+  </si>
+  <si>
+    <t>Ribosomal protein S4</t>
+  </si>
+  <si>
+    <t>Promotes GDP–GTP exchange on EF-1α during translation elongation</t>
+  </si>
+  <si>
+    <t>Non-sequence-specific dsDNA- and RNA-binding protein involved in chromatin organization</t>
+  </si>
+  <si>
+    <t>OB-fold nucleic acid-binding domain</t>
+  </si>
+  <si>
+    <t>Primary rRNA-binding protein involved in 30S ribosome assembly</t>
+  </si>
+  <si>
+    <t>Unassigned multi-copy gene</t>
+  </si>
+  <si>
+    <t>OmcB</t>
+  </si>
+  <si>
+    <t>KSR</t>
+  </si>
+  <si>
+    <t>KSR1</t>
+  </si>
+  <si>
+    <t>RNA polymerases I/II/III subunit RPABC1</t>
+  </si>
+  <si>
+    <t>Required for pre-18S rRNA processing</t>
+  </si>
+  <si>
+    <t>Involved in SRP-mediated targeting of nascent membrane proteins</t>
+  </si>
+  <si>
+    <t>Required for dorsoventral patterning during early embryogenesis</t>
+  </si>
+  <si>
+    <t>Exocyst subunit</t>
+  </si>
+  <si>
+    <t>Pyrophosphatase</t>
+  </si>
+  <si>
+    <t>Catalyzes glycyl-tRNA formation</t>
+  </si>
+  <si>
+    <t>ITGB1</t>
+  </si>
+  <si>
+    <t>Involved in 30S ribosomal subunit maturation</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -755,6 +761,12 @@
       <b/>
       <sz val="11"/>
       <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color indexed="8"/>
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
@@ -799,7 +811,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -807,6 +819,8 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1103,10 +1117,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D235"/>
+  <dimension ref="A1:D237"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="38.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="32.6640625" customWidth="1"/>
     <col min="2" max="2" width="22.83203125" customWidth="1"/>
     <col min="3" max="3" width="23.6640625" customWidth="1"/>
     <col min="4" max="4" width="41.6640625" bestFit="1" customWidth="1"/>
@@ -1114,7 +1128,7 @@
   <sheetData>
     <row r="1" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>236</v>
+        <v>189</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
@@ -1273,7 +1287,7 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
-        <v>14</v>
+        <v>211</v>
       </c>
       <c r="B13" s="1">
         <v>1</v>
@@ -1287,7 +1301,7 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B14" s="1">
         <v>1</v>
@@ -1301,7 +1315,7 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
-        <v>16</v>
+        <v>212</v>
       </c>
       <c r="B15" s="1">
         <v>4</v>
@@ -1315,7 +1329,7 @@
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B16" s="1">
         <v>2</v>
@@ -1329,7 +1343,7 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B17" s="1">
         <v>2</v>
@@ -1343,7 +1357,7 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B18" s="1">
         <v>2</v>
@@ -1357,7 +1371,7 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B19" s="1">
         <v>6</v>
@@ -1371,7 +1385,7 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B20" s="1">
         <v>6</v>
@@ -1385,7 +1399,7 @@
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B21" s="1">
         <v>3</v>
@@ -1399,7 +1413,7 @@
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B22" s="1">
         <v>11</v>
@@ -1413,7 +1427,7 @@
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
-        <v>24</v>
+        <v>213</v>
       </c>
       <c r="B23" s="1">
         <v>9</v>
@@ -1427,7 +1441,7 @@
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B24" s="1">
         <v>5</v>
@@ -1441,7 +1455,7 @@
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B25" s="1">
         <v>6</v>
@@ -1455,349 +1469,349 @@
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
-        <v>27</v>
+        <v>214</v>
       </c>
       <c r="B26" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C26" s="1">
-        <v>7</v>
-      </c>
-      <c r="D26" s="5">
-        <v>12.5</v>
+        <v>6</v>
+      </c>
+      <c r="D26" s="8">
+        <v>14.285714285714279</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
-        <v>28</v>
+        <v>215</v>
       </c>
       <c r="B27" s="1">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C27" s="1">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D27" s="5">
-        <v>11.1111111111111</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="B28" s="1">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C28" s="1">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D28" s="5">
-        <v>10</v>
+        <v>11.1111111111111</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
-        <v>30</v>
+        <v>216</v>
       </c>
       <c r="B29" s="1">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C29" s="1">
+        <v>9</v>
+      </c>
+      <c r="D29" s="5">
         <v>10</v>
-      </c>
-      <c r="D29" s="5">
-        <v>9.0909090909090899</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
-        <v>31</v>
+        <v>217</v>
       </c>
       <c r="B30" s="1">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="C30" s="1">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="D30" s="5">
-        <v>8.5714285714285694</v>
+        <v>9.0909090909090899</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="B31" s="1">
+        <v>35</v>
+      </c>
+      <c r="C31" s="1">
         <v>32</v>
       </c>
-      <c r="B31" s="1">
-        <v>15</v>
-      </c>
-      <c r="C31" s="1">
-        <v>14</v>
-      </c>
       <c r="D31" s="5">
-        <v>6.6666666666666696</v>
+        <v>8.5714285714285694</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="B32" s="1">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="C32" s="1">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="D32" s="5">
-        <v>5.8823529411764701</v>
+        <v>6.6666666666666696</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B33" s="1">
         <v>34</v>
       </c>
-      <c r="B33" s="1">
-        <v>21</v>
-      </c>
       <c r="C33" s="1">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="D33" s="5">
-        <v>4.7619047619047601</v>
+        <v>5.8823529411764701</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="B34" s="1">
-        <v>44</v>
+        <v>21</v>
       </c>
       <c r="C34" s="1">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="D34" s="5">
-        <v>4.5454545454545503</v>
+        <v>4.7619047619047601</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A35" s="1" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="B35" s="1">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="C35" s="1">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="D35" s="5">
-        <v>2.8571428571428599</v>
+        <v>4.5454545454545503</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="B36" s="1">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C36" s="1">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D36" s="5">
-        <v>2.6315789473684199</v>
+        <v>2.8571428571428599</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A37" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B37" s="1">
         <v>38</v>
       </c>
-      <c r="B37" s="1">
-        <v>117</v>
-      </c>
       <c r="C37" s="1">
-        <v>114</v>
+        <v>37</v>
       </c>
       <c r="D37" s="5">
-        <v>2.5641025641025599</v>
+        <v>2.6315789473684199</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A38" s="1" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="B38" s="1">
-        <v>88</v>
+        <v>117</v>
       </c>
       <c r="C38" s="1">
-        <v>86</v>
+        <v>114</v>
       </c>
       <c r="D38" s="5">
-        <v>2.2727272727272698</v>
+        <v>2.5641025641025599</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A39" s="1" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="B39" s="1">
-        <v>109</v>
+        <v>88</v>
       </c>
       <c r="C39" s="1">
-        <v>107</v>
+        <v>86</v>
       </c>
       <c r="D39" s="5">
-        <v>1.8348623853210999</v>
+        <v>2.2727272727272698</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A40" s="1" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="B40" s="1">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C40" s="1">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="D40" s="5">
-        <v>1.8018018018018001</v>
+        <v>1.8348623853210999</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
-        <v>42</v>
+        <v>190</v>
       </c>
       <c r="B41" s="1">
-        <v>67</v>
+        <v>111</v>
       </c>
       <c r="C41" s="1">
-        <v>66</v>
+        <v>109</v>
       </c>
       <c r="D41" s="5">
-        <v>1.4925373134328399</v>
+        <v>1.8018018018018001</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A42" s="1" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="B42" s="1">
-        <v>429</v>
+        <v>67</v>
       </c>
       <c r="C42" s="1">
-        <v>426</v>
+        <v>66</v>
       </c>
       <c r="D42" s="5">
-        <v>0.69930069930069905</v>
+        <v>1.4925373134328399</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A43" s="1" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="B43" s="1">
-        <v>336</v>
+        <v>429</v>
       </c>
       <c r="C43" s="1">
-        <v>333</v>
+        <v>426</v>
       </c>
       <c r="D43" s="5">
-        <v>0.89285714285714302</v>
+        <v>0.69930069930069905</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="B44" s="1">
-        <v>129</v>
+        <v>336</v>
       </c>
       <c r="C44" s="1">
-        <v>128</v>
+        <v>333</v>
       </c>
       <c r="D44" s="5">
-        <v>0.775193798449612</v>
+        <v>0.89285714285714302</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A45" s="1" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="B45" s="1">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="C45" s="1">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="D45" s="5">
-        <v>0.72992700729926996</v>
+        <v>0.775193798449612</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A46" s="1" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="B46" s="1">
-        <v>153</v>
+        <v>137</v>
       </c>
       <c r="C46" s="1">
-        <v>152</v>
+        <v>136</v>
       </c>
       <c r="D46" s="5">
-        <v>0.65359477124182996</v>
+        <v>0.72992700729926996</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A47" s="1" t="s">
-        <v>48</v>
+        <v>219</v>
       </c>
       <c r="B47" s="1">
-        <v>213</v>
+        <v>153</v>
       </c>
       <c r="C47" s="1">
-        <v>212</v>
+        <v>152</v>
       </c>
       <c r="D47" s="5">
-        <v>0.46948356807511699</v>
+        <v>0.65359477124182996</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A48" s="1" t="s">
-        <v>49</v>
+        <v>220</v>
       </c>
       <c r="B48" s="1">
-        <v>238</v>
+        <v>213</v>
       </c>
       <c r="C48" s="1">
-        <v>237</v>
+        <v>212</v>
       </c>
       <c r="D48" s="5">
-        <v>0.42016806722689098</v>
+        <v>0.46948356807511699</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A49" s="1" t="s">
-        <v>50</v>
+        <v>221</v>
       </c>
       <c r="B49" s="1">
-        <v>208</v>
+        <v>238</v>
       </c>
       <c r="C49" s="1">
-        <v>208</v>
+        <v>237</v>
       </c>
       <c r="D49" s="5">
-        <v>0</v>
+        <v>0.42016806722689098</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A50" s="1" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="B50" s="1">
-        <v>151</v>
+        <v>208</v>
       </c>
       <c r="C50" s="1">
-        <v>151</v>
+        <v>208</v>
       </c>
       <c r="D50" s="5">
         <v>0</v>
@@ -1805,13 +1819,13 @@
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A51" s="1" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="B51" s="1">
-        <v>120</v>
+        <v>151</v>
       </c>
       <c r="C51" s="1">
-        <v>120</v>
+        <v>151</v>
       </c>
       <c r="D51" s="5">
         <v>0</v>
@@ -1819,13 +1833,13 @@
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A52" s="1" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="B52" s="1">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="C52" s="1">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="D52" s="5">
         <v>0</v>
@@ -1833,13 +1847,13 @@
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A53" s="1" t="s">
-        <v>54</v>
+        <v>191</v>
       </c>
       <c r="B53" s="1">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="C53" s="1">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="D53" s="5">
         <v>0</v>
@@ -1847,13 +1861,13 @@
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A54" s="1" t="s">
-        <v>55</v>
+        <v>192</v>
       </c>
       <c r="B54" s="1">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="C54" s="1">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="D54" s="5">
         <v>0</v>
@@ -1861,13 +1875,13 @@
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A55" s="1" t="s">
-        <v>56</v>
+        <v>42</v>
       </c>
       <c r="B55" s="1">
-        <v>87</v>
+        <v>105</v>
       </c>
       <c r="C55" s="1">
-        <v>87</v>
+        <v>105</v>
       </c>
       <c r="D55" s="5">
         <v>0</v>
@@ -1875,13 +1889,13 @@
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A56" s="1" t="s">
-        <v>57</v>
+        <v>43</v>
       </c>
       <c r="B56" s="1">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="C56" s="1">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="D56" s="5">
         <v>0</v>
@@ -1889,13 +1903,13 @@
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A57" s="1" t="s">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="B57" s="1">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="C57" s="1">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="D57" s="5">
         <v>0</v>
@@ -1903,13 +1917,13 @@
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A58" s="1" t="s">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="B58" s="1">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="C58" s="1">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="D58" s="5">
         <v>0</v>
@@ -1917,13 +1931,13 @@
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A59" s="1" t="s">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="B59" s="1">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="C59" s="1">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="D59" s="5">
         <v>0</v>
@@ -1931,7 +1945,7 @@
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A60" s="1" t="s">
-        <v>61</v>
+        <v>193</v>
       </c>
       <c r="B60" s="1">
         <v>62</v>
@@ -1945,13 +1959,13 @@
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A61" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B61" s="1">
         <v>62</v>
       </c>
-      <c r="B61" s="1">
-        <v>88</v>
-      </c>
       <c r="C61" s="1">
-        <v>88</v>
+        <v>62</v>
       </c>
       <c r="D61" s="5">
         <v>0</v>
@@ -1959,13 +1973,13 @@
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A62" s="1" t="s">
-        <v>63</v>
+        <v>194</v>
       </c>
       <c r="B62" s="1">
-        <v>52</v>
+        <v>88</v>
       </c>
       <c r="C62" s="1">
-        <v>52</v>
+        <v>88</v>
       </c>
       <c r="D62" s="5">
         <v>0</v>
@@ -1973,13 +1987,13 @@
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A63" s="1" t="s">
-        <v>64</v>
+        <v>48</v>
       </c>
       <c r="B63" s="1">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="C63" s="1">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="D63" s="5">
         <v>0</v>
@@ -1987,7 +2001,7 @@
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A64" s="1" t="s">
-        <v>65</v>
+        <v>222</v>
       </c>
       <c r="B64" s="1">
         <v>36</v>
@@ -2001,13 +2015,13 @@
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A65" s="1" t="s">
-        <v>66</v>
+        <v>49</v>
       </c>
       <c r="B65" s="1">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C65" s="1">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="D65" s="5">
         <v>0</v>
@@ -2015,13 +2029,13 @@
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A66" s="1" t="s">
-        <v>67</v>
+        <v>223</v>
       </c>
       <c r="B66" s="1">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="C66" s="1">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D66" s="5">
         <v>0</v>
@@ -2029,7 +2043,7 @@
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A67" s="1" t="s">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="B67" s="1">
         <v>29</v>
@@ -2043,13 +2057,13 @@
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A68" s="1" t="s">
-        <v>69</v>
+        <v>51</v>
       </c>
       <c r="B68" s="1">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C68" s="1">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="D68" s="5">
         <v>0</v>
@@ -2057,7 +2071,7 @@
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A69" s="1" t="s">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="B69" s="1">
         <v>26</v>
@@ -2071,13 +2085,13 @@
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A70" s="1" t="s">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="B70" s="1">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="C70" s="1">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="D70" s="5">
         <v>0</v>
@@ -2085,13 +2099,13 @@
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A71" s="1" t="s">
-        <v>72</v>
+        <v>54</v>
       </c>
       <c r="B71" s="1">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C71" s="1">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D71" s="5">
         <v>0</v>
@@ -2099,13 +2113,13 @@
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A72" s="1" t="s">
-        <v>73</v>
+        <v>55</v>
       </c>
       <c r="B72" s="1">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C72" s="1">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D72" s="5">
         <v>0</v>
@@ -2113,13 +2127,13 @@
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A73" s="1" t="s">
-        <v>74</v>
+        <v>56</v>
       </c>
       <c r="B73" s="1">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C73" s="1">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D73" s="5">
         <v>0</v>
@@ -2127,13 +2141,13 @@
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A74" s="1" t="s">
-        <v>75</v>
+        <v>57</v>
       </c>
       <c r="B74" s="1">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C74" s="1">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D74" s="5">
         <v>0</v>
@@ -2141,13 +2155,13 @@
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A75" s="1" t="s">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="B75" s="1">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C75" s="1">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D75" s="5">
         <v>0</v>
@@ -2155,7 +2169,7 @@
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A76" s="1" t="s">
-        <v>77</v>
+        <v>59</v>
       </c>
       <c r="B76" s="1">
         <v>15</v>
@@ -2169,13 +2183,13 @@
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A77" s="1" t="s">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="B77" s="1">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C77" s="1">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D77" s="5">
         <v>0</v>
@@ -2183,13 +2197,13 @@
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A78" s="1" t="s">
-        <v>79</v>
+        <v>61</v>
       </c>
       <c r="B78" s="1">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C78" s="1">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D78" s="5">
         <v>0</v>
@@ -2197,13 +2211,13 @@
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A79" s="1" t="s">
-        <v>80</v>
+        <v>195</v>
       </c>
       <c r="B79" s="1">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C79" s="1">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D79" s="5">
         <v>0</v>
@@ -2211,7 +2225,7 @@
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A80" s="1" t="s">
-        <v>81</v>
+        <v>62</v>
       </c>
       <c r="B80" s="1">
         <v>12</v>
@@ -2225,13 +2239,13 @@
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A81" s="1" t="s">
-        <v>82</v>
+        <v>63</v>
       </c>
       <c r="B81" s="1">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C81" s="1">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D81" s="5">
         <v>0</v>
@@ -2239,7 +2253,7 @@
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A82" s="1" t="s">
-        <v>83</v>
+        <v>196</v>
       </c>
       <c r="B82" s="1">
         <v>11</v>
@@ -2253,7 +2267,7 @@
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A83" s="1" t="s">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="B83" s="1">
         <v>11</v>
@@ -2267,13 +2281,13 @@
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A84" s="1" t="s">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="B84" s="1">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C84" s="1">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D84" s="5">
         <v>0</v>
@@ -2281,7 +2295,7 @@
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A85" s="1" t="s">
-        <v>86</v>
+        <v>66</v>
       </c>
       <c r="B85" s="1">
         <v>10</v>
@@ -2295,7 +2309,7 @@
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A86" s="1" t="s">
-        <v>87</v>
+        <v>67</v>
       </c>
       <c r="B86" s="1">
         <v>10</v>
@@ -2309,7 +2323,7 @@
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A87" s="1" t="s">
-        <v>88</v>
+        <v>68</v>
       </c>
       <c r="B87" s="1">
         <v>10</v>
@@ -2323,7 +2337,7 @@
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A88" s="1" t="s">
-        <v>89</v>
+        <v>69</v>
       </c>
       <c r="B88" s="1">
         <v>10</v>
@@ -2337,7 +2351,7 @@
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A89" s="1" t="s">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="B89" s="1">
         <v>10</v>
@@ -2351,7 +2365,7 @@
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A90" s="1" t="s">
-        <v>91</v>
+        <v>71</v>
       </c>
       <c r="B90" s="1">
         <v>10</v>
@@ -2365,13 +2379,13 @@
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A91" s="1" t="s">
-        <v>92</v>
+        <v>72</v>
       </c>
       <c r="B91" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C91" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D91" s="5">
         <v>0</v>
@@ -2379,7 +2393,7 @@
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A92" s="1" t="s">
-        <v>93</v>
+        <v>73</v>
       </c>
       <c r="B92" s="1">
         <v>9</v>
@@ -2393,7 +2407,7 @@
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A93" s="1" t="s">
-        <v>94</v>
+        <v>74</v>
       </c>
       <c r="B93" s="1">
         <v>9</v>
@@ -2407,13 +2421,13 @@
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A94" s="1" t="s">
-        <v>95</v>
+        <v>75</v>
       </c>
       <c r="B94" s="1">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C94" s="1">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D94" s="5">
         <v>0</v>
@@ -2421,7 +2435,7 @@
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A95" s="1" t="s">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="B95" s="1">
         <v>8</v>
@@ -2435,13 +2449,13 @@
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A96" s="1" t="s">
-        <v>97</v>
+        <v>77</v>
       </c>
       <c r="B96" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C96" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D96" s="5">
         <v>0</v>
@@ -2449,7 +2463,7 @@
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A97" s="1" t="s">
-        <v>98</v>
+        <v>78</v>
       </c>
       <c r="B97" s="1">
         <v>7</v>
@@ -2463,7 +2477,7 @@
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A98" s="1" t="s">
-        <v>99</v>
+        <v>79</v>
       </c>
       <c r="B98" s="1">
         <v>7</v>
@@ -2477,7 +2491,7 @@
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A99" s="1" t="s">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="B99" s="1">
         <v>7</v>
@@ -2491,7 +2505,7 @@
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A100" s="1" t="s">
-        <v>101</v>
+        <v>81</v>
       </c>
       <c r="B100" s="1">
         <v>7</v>
@@ -2505,7 +2519,7 @@
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A101" s="1" t="s">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="B101" s="1">
         <v>7</v>
@@ -2519,7 +2533,7 @@
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A102" s="1" t="s">
-        <v>103</v>
+        <v>83</v>
       </c>
       <c r="B102" s="1">
         <v>7</v>
@@ -2533,13 +2547,13 @@
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A103" s="1" t="s">
-        <v>104</v>
+        <v>84</v>
       </c>
       <c r="B103" s="1">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C103" s="1">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D103" s="5">
         <v>0</v>
@@ -2547,7 +2561,7 @@
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A104" s="1" t="s">
-        <v>105</v>
+        <v>85</v>
       </c>
       <c r="B104" s="1">
         <v>6</v>
@@ -2561,7 +2575,7 @@
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A105" s="1" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
       <c r="B105" s="1">
         <v>6</v>
@@ -2575,13 +2589,13 @@
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A106" s="1" t="s">
-        <v>107</v>
+        <v>87</v>
       </c>
       <c r="B106" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C106" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D106" s="5">
         <v>0</v>
@@ -2589,13 +2603,13 @@
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A107" s="1" t="s">
-        <v>108</v>
+        <v>88</v>
       </c>
       <c r="B107" s="1">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C107" s="1">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D107" s="5">
         <v>0</v>
@@ -2603,13 +2617,13 @@
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A108" s="1" t="s">
-        <v>109</v>
+        <v>89</v>
       </c>
       <c r="B108" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C108" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D108" s="5">
         <v>0</v>
@@ -2617,7 +2631,7 @@
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A109" s="1" t="s">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="B109" s="1">
         <v>5</v>
@@ -2631,7 +2645,7 @@
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A110" s="1" t="s">
-        <v>111</v>
+        <v>91</v>
       </c>
       <c r="B110" s="1">
         <v>5</v>
@@ -2645,7 +2659,7 @@
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A111" s="1" t="s">
-        <v>112</v>
+        <v>92</v>
       </c>
       <c r="B111" s="1">
         <v>5</v>
@@ -2659,7 +2673,7 @@
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A112" s="1" t="s">
-        <v>113</v>
+        <v>93</v>
       </c>
       <c r="B112" s="1">
         <v>5</v>
@@ -2673,7 +2687,7 @@
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A113" s="1" t="s">
-        <v>114</v>
+        <v>94</v>
       </c>
       <c r="B113" s="1">
         <v>5</v>
@@ -2687,7 +2701,7 @@
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A114" s="1" t="s">
-        <v>115</v>
+        <v>95</v>
       </c>
       <c r="B114" s="1">
         <v>5</v>
@@ -2701,7 +2715,7 @@
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A115" s="1" t="s">
-        <v>116</v>
+        <v>96</v>
       </c>
       <c r="B115" s="1">
         <v>5</v>
@@ -2715,13 +2729,13 @@
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A116" s="1" t="s">
-        <v>117</v>
+        <v>97</v>
       </c>
       <c r="B116" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C116" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D116" s="5">
         <v>0</v>
@@ -2729,7 +2743,7 @@
     </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A117" s="1" t="s">
-        <v>118</v>
+        <v>98</v>
       </c>
       <c r="B117" s="1">
         <v>4</v>
@@ -2743,13 +2757,13 @@
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A118" s="1" t="s">
-        <v>119</v>
+        <v>99</v>
       </c>
       <c r="B118" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C118" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D118" s="5">
         <v>0</v>
@@ -2757,13 +2771,13 @@
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A119" s="1" t="s">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="B119" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C119" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D119" s="5">
         <v>0</v>
@@ -2771,7 +2785,7 @@
     </row>
     <row r="120" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A120" s="1" t="s">
-        <v>121</v>
+        <v>197</v>
       </c>
       <c r="B120" s="1">
         <v>4</v>
@@ -2785,7 +2799,7 @@
     </row>
     <row r="121" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A121" s="1" t="s">
-        <v>122</v>
+        <v>101</v>
       </c>
       <c r="B121" s="1">
         <v>4</v>
@@ -2799,7 +2813,7 @@
     </row>
     <row r="122" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A122" s="1" t="s">
-        <v>123</v>
+        <v>198</v>
       </c>
       <c r="B122" s="1">
         <v>4</v>
@@ -2813,7 +2827,7 @@
     </row>
     <row r="123" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A123" s="1" t="s">
-        <v>124</v>
+        <v>102</v>
       </c>
       <c r="B123" s="1">
         <v>4</v>
@@ -2827,7 +2841,7 @@
     </row>
     <row r="124" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A124" s="1" t="s">
-        <v>125</v>
+        <v>103</v>
       </c>
       <c r="B124" s="1">
         <v>4</v>
@@ -2841,7 +2855,7 @@
     </row>
     <row r="125" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A125" s="1" t="s">
-        <v>126</v>
+        <v>104</v>
       </c>
       <c r="B125" s="1">
         <v>4</v>
@@ -2855,7 +2869,7 @@
     </row>
     <row r="126" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A126" s="1" t="s">
-        <v>127</v>
+        <v>199</v>
       </c>
       <c r="B126" s="1">
         <v>4</v>
@@ -2869,7 +2883,7 @@
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A127" s="1" t="s">
-        <v>128</v>
+        <v>105</v>
       </c>
       <c r="B127" s="1">
         <v>4</v>
@@ -2883,13 +2897,13 @@
     </row>
     <row r="128" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A128" s="1" t="s">
-        <v>129</v>
+        <v>106</v>
       </c>
       <c r="B128" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C128" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D128" s="5">
         <v>0</v>
@@ -2897,7 +2911,7 @@
     </row>
     <row r="129" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A129" s="1" t="s">
-        <v>130</v>
+        <v>107</v>
       </c>
       <c r="B129" s="1">
         <v>3</v>
@@ -2911,7 +2925,7 @@
     </row>
     <row r="130" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A130" s="1" t="s">
-        <v>131</v>
+        <v>108</v>
       </c>
       <c r="B130" s="1">
         <v>3</v>
@@ -2925,7 +2939,7 @@
     </row>
     <row r="131" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A131" s="1" t="s">
-        <v>132</v>
+        <v>109</v>
       </c>
       <c r="B131" s="1">
         <v>3</v>
@@ -2939,7 +2953,7 @@
     </row>
     <row r="132" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A132" s="1" t="s">
-        <v>133</v>
+        <v>110</v>
       </c>
       <c r="B132" s="1">
         <v>3</v>
@@ -2953,7 +2967,7 @@
     </row>
     <row r="133" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A133" s="1" t="s">
-        <v>134</v>
+        <v>200</v>
       </c>
       <c r="B133" s="1">
         <v>3</v>
@@ -2967,7 +2981,7 @@
     </row>
     <row r="134" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A134" s="1" t="s">
-        <v>135</v>
+        <v>111</v>
       </c>
       <c r="B134" s="1">
         <v>3</v>
@@ -2981,7 +2995,7 @@
     </row>
     <row r="135" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A135" s="1" t="s">
-        <v>136</v>
+        <v>112</v>
       </c>
       <c r="B135" s="1">
         <v>3</v>
@@ -2995,7 +3009,7 @@
     </row>
     <row r="136" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A136" s="1" t="s">
-        <v>137</v>
+        <v>113</v>
       </c>
       <c r="B136" s="1">
         <v>3</v>
@@ -3009,7 +3023,7 @@
     </row>
     <row r="137" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A137" s="1" t="s">
-        <v>138</v>
+        <v>114</v>
       </c>
       <c r="B137" s="1">
         <v>3</v>
@@ -3023,7 +3037,7 @@
     </row>
     <row r="138" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A138" s="1" t="s">
-        <v>139</v>
+        <v>115</v>
       </c>
       <c r="B138" s="1">
         <v>3</v>
@@ -3037,7 +3051,7 @@
     </row>
     <row r="139" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A139" s="1" t="s">
-        <v>140</v>
+        <v>116</v>
       </c>
       <c r="B139" s="1">
         <v>3</v>
@@ -3051,7 +3065,7 @@
     </row>
     <row r="140" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A140" s="1" t="s">
-        <v>141</v>
+        <v>117</v>
       </c>
       <c r="B140" s="1">
         <v>3</v>
@@ -3065,7 +3079,7 @@
     </row>
     <row r="141" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A141" s="1" t="s">
-        <v>142</v>
+        <v>118</v>
       </c>
       <c r="B141" s="1">
         <v>3</v>
@@ -3079,7 +3093,7 @@
     </row>
     <row r="142" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A142" s="1" t="s">
-        <v>143</v>
+        <v>119</v>
       </c>
       <c r="B142" s="1">
         <v>3</v>
@@ -3093,7 +3107,7 @@
     </row>
     <row r="143" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A143" s="1" t="s">
-        <v>144</v>
+        <v>120</v>
       </c>
       <c r="B143" s="1">
         <v>3</v>
@@ -3107,7 +3121,7 @@
     </row>
     <row r="144" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A144" s="1" t="s">
-        <v>145</v>
+        <v>121</v>
       </c>
       <c r="B144" s="1">
         <v>3</v>
@@ -3121,7 +3135,7 @@
     </row>
     <row r="145" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A145" s="1" t="s">
-        <v>146</v>
+        <v>122</v>
       </c>
       <c r="B145" s="1">
         <v>3</v>
@@ -3135,7 +3149,7 @@
     </row>
     <row r="146" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A146" s="1" t="s">
-        <v>147</v>
+        <v>123</v>
       </c>
       <c r="B146" s="1">
         <v>3</v>
@@ -3149,7 +3163,7 @@
     </row>
     <row r="147" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A147" s="1" t="s">
-        <v>148</v>
+        <v>124</v>
       </c>
       <c r="B147" s="1">
         <v>3</v>
@@ -3163,7 +3177,7 @@
     </row>
     <row r="148" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A148" s="1" t="s">
-        <v>149</v>
+        <v>125</v>
       </c>
       <c r="B148" s="1">
         <v>3</v>
@@ -3177,13 +3191,13 @@
     </row>
     <row r="149" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A149" s="1" t="s">
-        <v>150</v>
+        <v>126</v>
       </c>
       <c r="B149" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C149" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D149" s="5">
         <v>0</v>
@@ -3191,7 +3205,7 @@
     </row>
     <row r="150" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A150" s="1" t="s">
-        <v>151</v>
+        <v>127</v>
       </c>
       <c r="B150" s="1">
         <v>2</v>
@@ -3205,13 +3219,13 @@
     </row>
     <row r="151" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A151" s="1" t="s">
-        <v>152</v>
+        <v>224</v>
       </c>
       <c r="B151" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C151" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D151" s="5">
         <v>0</v>
@@ -3219,13 +3233,13 @@
     </row>
     <row r="152" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A152" s="1" t="s">
-        <v>153</v>
+        <v>128</v>
       </c>
       <c r="B152" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C152" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D152" s="5">
         <v>0</v>
@@ -3233,7 +3247,7 @@
     </row>
     <row r="153" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A153" s="1" t="s">
-        <v>154</v>
+        <v>129</v>
       </c>
       <c r="B153" s="1">
         <v>2</v>
@@ -3247,7 +3261,7 @@
     </row>
     <row r="154" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A154" s="1" t="s">
-        <v>155</v>
+        <v>130</v>
       </c>
       <c r="B154" s="1">
         <v>2</v>
@@ -3261,7 +3275,7 @@
     </row>
     <row r="155" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A155" s="1" t="s">
-        <v>156</v>
+        <v>131</v>
       </c>
       <c r="B155" s="1">
         <v>2</v>
@@ -3275,7 +3289,7 @@
     </row>
     <row r="156" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A156" s="1" t="s">
-        <v>157</v>
+        <v>132</v>
       </c>
       <c r="B156" s="1">
         <v>2</v>
@@ -3289,7 +3303,7 @@
     </row>
     <row r="157" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A157" s="1" t="s">
-        <v>158</v>
+        <v>133</v>
       </c>
       <c r="B157" s="1">
         <v>2</v>
@@ -3303,7 +3317,7 @@
     </row>
     <row r="158" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A158" s="1" t="s">
-        <v>159</v>
+        <v>134</v>
       </c>
       <c r="B158" s="1">
         <v>2</v>
@@ -3317,7 +3331,7 @@
     </row>
     <row r="159" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A159" s="1" t="s">
-        <v>234</v>
+        <v>135</v>
       </c>
       <c r="B159" s="1">
         <v>2</v>
@@ -3331,7 +3345,7 @@
     </row>
     <row r="160" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A160" s="1" t="s">
-        <v>160</v>
+        <v>187</v>
       </c>
       <c r="B160" s="1">
         <v>2</v>
@@ -3345,7 +3359,7 @@
     </row>
     <row r="161" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A161" s="1" t="s">
-        <v>161</v>
+        <v>136</v>
       </c>
       <c r="B161" s="1">
         <v>2</v>
@@ -3359,7 +3373,7 @@
     </row>
     <row r="162" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A162" s="1" t="s">
-        <v>162</v>
+        <v>137</v>
       </c>
       <c r="B162" s="1">
         <v>2</v>
@@ -3373,7 +3387,7 @@
     </row>
     <row r="163" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A163" s="1" t="s">
-        <v>163</v>
+        <v>138</v>
       </c>
       <c r="B163" s="1">
         <v>2</v>
@@ -3387,7 +3401,7 @@
     </row>
     <row r="164" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A164" s="1" t="s">
-        <v>164</v>
+        <v>139</v>
       </c>
       <c r="B164" s="1">
         <v>2</v>
@@ -3401,7 +3415,7 @@
     </row>
     <row r="165" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A165" s="1" t="s">
-        <v>165</v>
+        <v>140</v>
       </c>
       <c r="B165" s="1">
         <v>2</v>
@@ -3415,7 +3429,7 @@
     </row>
     <row r="166" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A166" s="1" t="s">
-        <v>166</v>
+        <v>141</v>
       </c>
       <c r="B166" s="1">
         <v>2</v>
@@ -3429,13 +3443,13 @@
     </row>
     <row r="167" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A167" s="1" t="s">
-        <v>167</v>
+        <v>142</v>
       </c>
       <c r="B167" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C167" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D167" s="5">
         <v>0</v>
@@ -3443,13 +3457,13 @@
     </row>
     <row r="168" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A168" s="1" t="s">
-        <v>168</v>
+        <v>143</v>
       </c>
       <c r="B168" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C168" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D168" s="5">
         <v>0</v>
@@ -3457,7 +3471,7 @@
     </row>
     <row r="169" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A169" s="1" t="s">
-        <v>169</v>
+        <v>201</v>
       </c>
       <c r="B169" s="1">
         <v>2</v>
@@ -3471,7 +3485,7 @@
     </row>
     <row r="170" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A170" s="1" t="s">
-        <v>170</v>
+        <v>202</v>
       </c>
       <c r="B170" s="1">
         <v>2</v>
@@ -3485,7 +3499,7 @@
     </row>
     <row r="171" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A171" s="1" t="s">
-        <v>171</v>
+        <v>144</v>
       </c>
       <c r="B171" s="1">
         <v>2</v>
@@ -3499,7 +3513,7 @@
     </row>
     <row r="172" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A172" s="1" t="s">
-        <v>172</v>
+        <v>145</v>
       </c>
       <c r="B172" s="1">
         <v>2</v>
@@ -3513,7 +3527,7 @@
     </row>
     <row r="173" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A173" s="1" t="s">
-        <v>173</v>
+        <v>225</v>
       </c>
       <c r="B173" s="1">
         <v>2</v>
@@ -3527,7 +3541,7 @@
     </row>
     <row r="174" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A174" s="1" t="s">
-        <v>174</v>
+        <v>146</v>
       </c>
       <c r="B174" s="1">
         <v>2</v>
@@ -3541,7 +3555,7 @@
     </row>
     <row r="175" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A175" s="1" t="s">
-        <v>175</v>
+        <v>147</v>
       </c>
       <c r="B175" s="1">
         <v>2</v>
@@ -3555,13 +3569,13 @@
     </row>
     <row r="176" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A176" s="1" t="s">
-        <v>176</v>
+        <v>148</v>
       </c>
       <c r="B176" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C176" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D176" s="5">
         <v>0</v>
@@ -3569,7 +3583,7 @@
     </row>
     <row r="177" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A177" s="1" t="s">
-        <v>177</v>
+        <v>149</v>
       </c>
       <c r="B177" s="1">
         <v>1</v>
@@ -3583,7 +3597,7 @@
     </row>
     <row r="178" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A178" s="1" t="s">
-        <v>178</v>
+        <v>150</v>
       </c>
       <c r="B178" s="1">
         <v>1</v>
@@ -3597,7 +3611,7 @@
     </row>
     <row r="179" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A179" s="1" t="s">
-        <v>179</v>
+        <v>151</v>
       </c>
       <c r="B179" s="1">
         <v>1</v>
@@ -3611,7 +3625,7 @@
     </row>
     <row r="180" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A180" s="1" t="s">
-        <v>180</v>
+        <v>152</v>
       </c>
       <c r="B180" s="1">
         <v>1</v>
@@ -3625,7 +3639,7 @@
     </row>
     <row r="181" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A181" s="1" t="s">
-        <v>181</v>
+        <v>153</v>
       </c>
       <c r="B181" s="1">
         <v>1</v>
@@ -3639,7 +3653,7 @@
     </row>
     <row r="182" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A182" s="1" t="s">
-        <v>182</v>
+        <v>154</v>
       </c>
       <c r="B182" s="1">
         <v>1</v>
@@ -3653,7 +3667,7 @@
     </row>
     <row r="183" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A183" s="1" t="s">
-        <v>183</v>
+        <v>155</v>
       </c>
       <c r="B183" s="1">
         <v>1</v>
@@ -3667,13 +3681,13 @@
     </row>
     <row r="184" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A184" s="1" t="s">
-        <v>184</v>
+        <v>156</v>
       </c>
       <c r="B184" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C184" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D184" s="5">
         <v>0</v>
@@ -3681,13 +3695,13 @@
     </row>
     <row r="185" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A185" s="1" t="s">
-        <v>185</v>
+        <v>157</v>
       </c>
       <c r="B185" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C185" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D185" s="5">
         <v>0</v>
@@ -3695,7 +3709,7 @@
     </row>
     <row r="186" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A186" s="1" t="s">
-        <v>186</v>
+        <v>158</v>
       </c>
       <c r="B186" s="1">
         <v>1</v>
@@ -3709,7 +3723,7 @@
     </row>
     <row r="187" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A187" s="1" t="s">
-        <v>187</v>
+        <v>203</v>
       </c>
       <c r="B187" s="1">
         <v>1</v>
@@ -3723,7 +3737,7 @@
     </row>
     <row r="188" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A188" s="1" t="s">
-        <v>188</v>
+        <v>159</v>
       </c>
       <c r="B188" s="1">
         <v>1</v>
@@ -3737,7 +3751,7 @@
     </row>
     <row r="189" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A189" s="1" t="s">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="B189" s="1">
         <v>1</v>
@@ -3751,7 +3765,7 @@
     </row>
     <row r="190" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A190" s="1" t="s">
-        <v>190</v>
+        <v>160</v>
       </c>
       <c r="B190" s="1">
         <v>1</v>
@@ -3765,7 +3779,7 @@
     </row>
     <row r="191" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A191" s="1" t="s">
-        <v>191</v>
+        <v>161</v>
       </c>
       <c r="B191" s="1">
         <v>1</v>
@@ -3779,7 +3793,7 @@
     </row>
     <row r="192" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A192" s="1" t="s">
-        <v>192</v>
+        <v>162</v>
       </c>
       <c r="B192" s="1">
         <v>1</v>
@@ -3793,7 +3807,7 @@
     </row>
     <row r="193" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A193" s="1" t="s">
-        <v>193</v>
+        <v>205</v>
       </c>
       <c r="B193" s="1">
         <v>1</v>
@@ -3807,7 +3821,7 @@
     </row>
     <row r="194" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A194" s="1" t="s">
-        <v>194</v>
+        <v>163</v>
       </c>
       <c r="B194" s="1">
         <v>1</v>
@@ -3821,7 +3835,7 @@
     </row>
     <row r="195" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A195" s="1" t="s">
-        <v>195</v>
+        <v>164</v>
       </c>
       <c r="B195" s="1">
         <v>1</v>
@@ -3835,7 +3849,7 @@
     </row>
     <row r="196" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A196" s="1" t="s">
-        <v>196</v>
+        <v>165</v>
       </c>
       <c r="B196" s="1">
         <v>1</v>
@@ -3849,7 +3863,7 @@
     </row>
     <row r="197" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A197" s="1" t="s">
-        <v>197</v>
+        <v>166</v>
       </c>
       <c r="B197" s="1">
         <v>1</v>
@@ -3863,7 +3877,7 @@
     </row>
     <row r="198" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A198" s="1" t="s">
-        <v>198</v>
+        <v>206</v>
       </c>
       <c r="B198" s="1">
         <v>1</v>
@@ -3876,8 +3890,8 @@
       </c>
     </row>
     <row r="199" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A199" s="1" t="s">
-        <v>199</v>
+      <c r="A199" s="7" t="s">
+        <v>207</v>
       </c>
       <c r="B199" s="1">
         <v>1</v>
@@ -3891,7 +3905,7 @@
     </row>
     <row r="200" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A200" s="1" t="s">
-        <v>200</v>
+        <v>167</v>
       </c>
       <c r="B200" s="1">
         <v>1</v>
@@ -3905,7 +3919,7 @@
     </row>
     <row r="201" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A201" s="1" t="s">
-        <v>201</v>
+        <v>168</v>
       </c>
       <c r="B201" s="1">
         <v>1</v>
@@ -3919,7 +3933,7 @@
     </row>
     <row r="202" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A202" s="1" t="s">
-        <v>202</v>
+        <v>226</v>
       </c>
       <c r="B202" s="1">
         <v>1</v>
@@ -3933,7 +3947,7 @@
     </row>
     <row r="203" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A203" s="1" t="s">
-        <v>203</v>
+        <v>169</v>
       </c>
       <c r="B203" s="1">
         <v>1</v>
@@ -3947,13 +3961,13 @@
     </row>
     <row r="204" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A204" s="1" t="s">
-        <v>204</v>
+        <v>227</v>
       </c>
       <c r="B204" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C204" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D204" s="5">
         <v>0</v>
@@ -3961,7 +3975,7 @@
     </row>
     <row r="205" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A205" s="1" t="s">
-        <v>205</v>
+        <v>228</v>
       </c>
       <c r="B205" s="1">
         <v>1</v>
@@ -3975,7 +3989,7 @@
     </row>
     <row r="206" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A206" s="1" t="s">
-        <v>206</v>
+        <v>229</v>
       </c>
       <c r="B206" s="1">
         <v>1</v>
@@ -3989,7 +4003,7 @@
     </row>
     <row r="207" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A207" s="1" t="s">
-        <v>207</v>
+        <v>170</v>
       </c>
       <c r="B207" s="1">
         <v>1</v>
@@ -4003,7 +4017,7 @@
     </row>
     <row r="208" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A208" s="1" t="s">
-        <v>208</v>
+        <v>171</v>
       </c>
       <c r="B208" s="1">
         <v>1</v>
@@ -4017,7 +4031,7 @@
     </row>
     <row r="209" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A209" s="1" t="s">
-        <v>209</v>
+        <v>230</v>
       </c>
       <c r="B209" s="1">
         <v>1</v>
@@ -4031,7 +4045,7 @@
     </row>
     <row r="210" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A210" s="1" t="s">
-        <v>235</v>
+        <v>208</v>
       </c>
       <c r="B210" s="1">
         <v>1</v>
@@ -4045,7 +4059,7 @@
     </row>
     <row r="211" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A211" s="1" t="s">
-        <v>210</v>
+        <v>172</v>
       </c>
       <c r="B211" s="1">
         <v>1</v>
@@ -4059,7 +4073,7 @@
     </row>
     <row r="212" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A212" s="1" t="s">
-        <v>211</v>
+        <v>188</v>
       </c>
       <c r="B212" s="1">
         <v>1</v>
@@ -4073,13 +4087,13 @@
     </row>
     <row r="213" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A213" s="1" t="s">
-        <v>212</v>
+        <v>231</v>
       </c>
       <c r="B213" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C213" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D213" s="5">
         <v>0</v>
@@ -4087,7 +4101,7 @@
     </row>
     <row r="214" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A214" s="1" t="s">
-        <v>213</v>
+        <v>173</v>
       </c>
       <c r="B214" s="1">
         <v>1</v>
@@ -4101,13 +4115,13 @@
     </row>
     <row r="215" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A215" s="1" t="s">
-        <v>214</v>
+        <v>232</v>
       </c>
       <c r="B215" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C215" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D215" s="5">
         <v>0</v>
@@ -4115,7 +4129,7 @@
     </row>
     <row r="216" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A216" s="1" t="s">
-        <v>215</v>
+        <v>174</v>
       </c>
       <c r="B216" s="1">
         <v>1</v>
@@ -4129,7 +4143,7 @@
     </row>
     <row r="217" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A217" s="1" t="s">
-        <v>216</v>
+        <v>209</v>
       </c>
       <c r="B217" s="1">
         <v>1</v>
@@ -4143,7 +4157,7 @@
     </row>
     <row r="218" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A218" s="1" t="s">
-        <v>217</v>
+        <v>175</v>
       </c>
       <c r="B218" s="1">
         <v>1</v>
@@ -4157,7 +4171,7 @@
     </row>
     <row r="219" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A219" s="1" t="s">
-        <v>218</v>
+        <v>233</v>
       </c>
       <c r="B219" s="1">
         <v>1</v>
@@ -4171,7 +4185,7 @@
     </row>
     <row r="220" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A220" s="1" t="s">
-        <v>219</v>
+        <v>176</v>
       </c>
       <c r="B220" s="1">
         <v>1</v>
@@ -4185,7 +4199,7 @@
     </row>
     <row r="221" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A221" s="1" t="s">
-        <v>220</v>
+        <v>177</v>
       </c>
       <c r="B221" s="1">
         <v>1</v>
@@ -4199,7 +4213,7 @@
     </row>
     <row r="222" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A222" s="1" t="s">
-        <v>221</v>
+        <v>178</v>
       </c>
       <c r="B222" s="1">
         <v>1</v>
@@ -4213,7 +4227,7 @@
     </row>
     <row r="223" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A223" s="1" t="s">
-        <v>222</v>
+        <v>210</v>
       </c>
       <c r="B223" s="1">
         <v>1</v>
@@ -4227,7 +4241,7 @@
     </row>
     <row r="224" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A224" s="1" t="s">
-        <v>223</v>
+        <v>234</v>
       </c>
       <c r="B224" s="1">
         <v>1</v>
@@ -4241,7 +4255,7 @@
     </row>
     <row r="225" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A225" s="1" t="s">
-        <v>224</v>
+        <v>235</v>
       </c>
       <c r="B225" s="1">
         <v>1</v>
@@ -4255,7 +4269,7 @@
     </row>
     <row r="226" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A226" s="1" t="s">
-        <v>225</v>
+        <v>236</v>
       </c>
       <c r="B226" s="1">
         <v>1</v>
@@ -4269,7 +4283,7 @@
     </row>
     <row r="227" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A227" s="1" t="s">
-        <v>226</v>
+        <v>179</v>
       </c>
       <c r="B227" s="1">
         <v>1</v>
@@ -4283,7 +4297,7 @@
     </row>
     <row r="228" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A228" s="1" t="s">
-        <v>227</v>
+        <v>237</v>
       </c>
       <c r="B228" s="1">
         <v>1</v>
@@ -4297,7 +4311,7 @@
     </row>
     <row r="229" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A229" s="1" t="s">
-        <v>228</v>
+        <v>180</v>
       </c>
       <c r="B229" s="1">
         <v>1</v>
@@ -4311,7 +4325,7 @@
     </row>
     <row r="230" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A230" s="1" t="s">
-        <v>229</v>
+        <v>238</v>
       </c>
       <c r="B230" s="1">
         <v>1</v>
@@ -4325,7 +4339,7 @@
     </row>
     <row r="231" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A231" s="1" t="s">
-        <v>230</v>
+        <v>181</v>
       </c>
       <c r="B231" s="1">
         <v>1</v>
@@ -4339,7 +4353,7 @@
     </row>
     <row r="232" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A232" s="1" t="s">
-        <v>231</v>
+        <v>182</v>
       </c>
       <c r="B232" s="1">
         <v>1</v>
@@ -4353,7 +4367,7 @@
     </row>
     <row r="233" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A233" s="1" t="s">
-        <v>232</v>
+        <v>183</v>
       </c>
       <c r="B233" s="1">
         <v>1</v>
@@ -4365,21 +4379,49 @@
         <v>0</v>
       </c>
     </row>
-    <row r="234" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A234" s="4" t="s">
-        <v>233</v>
-      </c>
-      <c r="B234" s="4">
-        <v>1</v>
-      </c>
-      <c r="C234" s="4">
-        <v>1</v>
-      </c>
-      <c r="D234" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="235" spans="1:4" ht="16" thickTop="1" x14ac:dyDescent="0.2"/>
+    <row r="234" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A234" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="B234" s="1">
+        <v>1</v>
+      </c>
+      <c r="C234" s="1">
+        <v>1</v>
+      </c>
+      <c r="D234" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="235" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A235" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="B235" s="1">
+        <v>1</v>
+      </c>
+      <c r="C235" s="1">
+        <v>1</v>
+      </c>
+      <c r="D235" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="236" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A236" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="B236" s="4">
+        <v>1</v>
+      </c>
+      <c r="C236" s="4">
+        <v>1</v>
+      </c>
+      <c r="D236" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="237" spans="1:4" ht="16" thickTop="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
